--- a/KURIKULUM2026_REVISI/009E_RINGKASAN_CPL_LENGKAP_PEMETAAN_BoK.xlsx
+++ b/KURIKULUM2026_REVISI/009E_RINGKASAN_CPL_LENGKAP_PEMETAAN_BoK.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -1082,7 +1082,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2. MATRIKS SILANG CPL ↔ 19 BAHAN KAJIAN (BoK) IS2020 (APTIKOM v2.0)</t>
+          <t>2. MATRIKS SILANG CPL ↔ 21 BAHAN KAJIAN (BoK) IS2020 (APTIKOM v2.0)</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1877,184 +1877,204 @@
       <c r="O40" s="8" t="inlineStr"/>
       <c r="P40" s="8" t="inlineStr"/>
     </row>
-    <row r="41"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>3. MATRIKS SILANG CPL ↔ 14 BAHAN KAJIAN UTAMA (BoK) IT2017 (APTIKOM)</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n"/>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
-      <c r="O42" s="4" t="n"/>
-      <c r="P42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>**BK-IS20**</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Ethics, Use and Implications for Society</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr"/>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>**BK-IS21**</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Internship and Professional Practice</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
+      <c r="J42" s="8" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr"/>
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="8" t="inlineStr"/>
+      <c r="O42" s="8" t="inlineStr"/>
+      <c r="P42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>3. MATRIKS SILANG CPL ↔ 15 BAHAN KAJIAN UTAMA (BoK) IT2017 (APTIKOM)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
+      <c r="P44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Kode BK</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Nama Bahan Kajian Utama IT2017</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="N45" s="6" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O43" s="6" t="inlineStr">
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P43" s="6" t="inlineStr">
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>**BK-IT01**</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Information Technology Fundamentals</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr"/>
-      <c r="O44" s="8" t="inlineStr"/>
-      <c r="P44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>**BK-IT02**</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Applied AI &amp; Intelligent Technologies</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr"/>
-      <c r="D45" s="9" t="inlineStr"/>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="10" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L45" s="10" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" s="10" t="inlineStr"/>
-      <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="10" t="inlineStr"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT03**</t>
+          <t>**BK-IT01**</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Networking &amp; Communications</t>
+          <t>Information Technology Fundamentals</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr"/>
@@ -2083,12 +2103,12 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>**BK-IT04**</t>
+          <t>**BK-IT02**</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Platform Technologies &amp; Web/Mobile</t>
+          <t>Applied AI &amp; Intelligent Technologies</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr"/>
@@ -2098,31 +2118,27 @@
       <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="10" t="inlineStr"/>
       <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
       <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O47" s="10" t="inlineStr"/>
       <c r="P47" s="10" t="inlineStr"/>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT05**</t>
+          <t>**BK-IT03**</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; Virtualization</t>
+          <t>Networking &amp; Communications</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr"/>
@@ -2151,12 +2167,12 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>**BK-IT06**</t>
+          <t>**BK-IT04**</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Cybersecurity Principles &amp; Defense</t>
+          <t>Platform Technologies &amp; Web/Mobile</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr"/>
@@ -2165,36 +2181,32 @@
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="10" t="inlineStr"/>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr"/>
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K49" s="10" t="inlineStr"/>
       <c r="L49" s="10" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N49" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O49" s="10" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
+      <c r="O49" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="P49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT07**</t>
+          <t>**BK-IT05**</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>System Integration and Architecture</t>
+          <t>Cloud Computing &amp; Virtualization</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr"/>
@@ -2217,22 +2229,18 @@
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr"/>
-      <c r="O50" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O50" s="8" t="inlineStr"/>
       <c r="P50" s="8" t="inlineStr"/>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>**BK-IT08**</t>
+          <t>**BK-IT06**</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>IT Service Management &amp; Governance</t>
+          <t>Cybersecurity Principles &amp; Defense</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr"/>
@@ -2249,7 +2257,11 @@
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="N51" s="10" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2261,12 +2273,12 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT09**</t>
+          <t>**BK-IT07**</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Information Visualization</t>
+          <t>System Integration and Architecture</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr"/>
@@ -2275,32 +2287,36 @@
       <c r="F52" s="8" t="inlineStr"/>
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr"/>
       <c r="K52" s="8" t="inlineStr"/>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="M52" s="8" t="inlineStr"/>
+      <c r="L52" s="8" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="N52" s="8" t="inlineStr"/>
-      <c r="O52" s="8" t="inlineStr"/>
+      <c r="O52" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="P52" s="8" t="inlineStr"/>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>**BK-IT10**</t>
+          <t>**BK-IT08**</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>User Experience &amp; Interaction Design</t>
+          <t>IT Service Management &amp; Governance</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr"/>
@@ -2309,32 +2325,32 @@
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" s="10" t="inlineStr"/>
-      <c r="O53" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O53" s="10" t="inlineStr"/>
       <c r="P53" s="10" t="inlineStr"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT11**</t>
+          <t>**BK-IT09**</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Software Development Practices</t>
+          <t>Data Analytics &amp; Information Visualization</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr"/>
@@ -2350,25 +2366,25 @@
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr"/>
-      <c r="L54" s="8" t="inlineStr"/>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
-      <c r="O54" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O54" s="8" t="inlineStr"/>
       <c r="P54" s="8" t="inlineStr"/>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>**BK-IT12**</t>
+          <t>**BK-IT10**</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>IT Risk Management and Compliance</t>
+          <t>User Experience &amp; Interaction Design</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr"/>
@@ -2378,27 +2394,31 @@
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="10" t="inlineStr"/>
       <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O55" s="10" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
+      <c r="O55" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="P55" s="10" t="inlineStr"/>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>**BK-IT13**</t>
+          <t>**BK-IT11**</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Technology Entrepreneurship</t>
+          <t>Software Development Practices</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr"/>
@@ -2408,27 +2428,31 @@
       <c r="G56" s="8" t="inlineStr"/>
       <c r="H56" s="8" t="inlineStr"/>
       <c r="I56" s="8" t="inlineStr"/>
-      <c r="J56" s="8" t="inlineStr"/>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K56" s="8" t="inlineStr"/>
       <c r="L56" s="8" t="inlineStr"/>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
-      <c r="O56" s="8" t="inlineStr"/>
-      <c r="P56" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P56" s="8" t="inlineStr"/>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>**BK-IT14**</t>
+          <t>**BK-IT12**</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>IoT and Embedded Smart Systems</t>
+          <t>IT Risk Management and Compliance</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr"/>
@@ -2439,741 +2463,843 @@
       <c r="H57" s="10" t="inlineStr"/>
       <c r="I57" s="10" t="inlineStr"/>
       <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="K57" s="10" t="inlineStr"/>
       <c r="L57" s="10" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O57" s="10" t="inlineStr"/>
       <c r="P57" s="10" t="inlineStr"/>
     </row>
-    <row r="58"/>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>**BK-IT13**</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Technology Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr"/>
+      <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr"/>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>**BK-IT14**</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>IoT and Embedded Smart Systems</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr"/>
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr"/>
+      <c r="G59" s="10" t="inlineStr"/>
+      <c r="H59" s="10" t="inlineStr"/>
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr"/>
+      <c r="P59" s="10" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>**BK-IT15**</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Global Professional Practice</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr"/>
+      <c r="L60" s="8" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="8" t="inlineStr"/>
+      <c r="O60" s="8" t="inlineStr"/>
+      <c r="P60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>4. MATRIKS PEMETAAN CPL ↔ 4 PROFIL LULUSAN (PL)</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
-      <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
-      <c r="O59" s="4" t="n"/>
-      <c r="P59" s="5" t="n"/>
-    </row>
-    <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Profil Lulusan</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Peminatan Terkait</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J60" s="6" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K60" s="6" t="inlineStr">
+      <c r="K63" s="6" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L60" s="6" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M60" s="6" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N60" s="6" t="inlineStr">
+      <c r="N63" s="6" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O60" s="6" t="inlineStr">
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P60" s="6" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>**PL-1: Intelligent IS Developer &amp; AI Engineer**</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K61" s="8" t="inlineStr">
+      <c r="K64" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr">
+      <c r="L64" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="M61" s="8" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="8" t="inlineStr"/>
+      <c r="O64" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="P61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="P64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>**PL-2: Cloud Infrastructure &amp; Cybersecurity Specialist**</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr"/>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr"/>
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="J62" s="10" t="inlineStr"/>
-      <c r="K62" s="10" t="inlineStr"/>
-      <c r="L62" s="10" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr">
+      <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr"/>
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="N62" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O62" s="10" t="inlineStr"/>
-      <c r="P62" s="10" t="inlineStr"/>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="O65" s="10" t="inlineStr"/>
+      <c r="P65" s="10" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>**PL-3: UI/UX Designer &amp; Digital Platform Engineer**</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr"/>
-      <c r="J63" s="8" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="8" t="inlineStr"/>
-      <c r="M63" s="8" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="8" t="inlineStr"/>
+      <c r="O66" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="P63" s="8" t="inlineStr">
+      <c r="P66" s="8" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>**PL-4: Digital Technopreneur &amp; IT Product Innovator**</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>P3 / P1 / P2</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr"/>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="G67" s="10" t="inlineStr"/>
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="J64" s="10" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K64" s="10" t="inlineStr">
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="L64" s="10" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" s="10" t="inlineStr"/>
-      <c r="O64" s="10" t="inlineStr">
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="P64" s="10" t="inlineStr">
+      <c r="P67" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="68"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>5. MATRIKS PEMETAAN CPL ↔ 3 JALUR PEMINATAN</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
-      <c r="O66" s="4" t="n"/>
-      <c r="P66" s="5" t="n"/>
-    </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="5" t="n"/>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Kode Peminatan</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Nomenklatur Jalur Peminatan</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="J70" s="6" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="K70" s="6" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr">
+      <c r="L70" s="6" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr">
+      <c r="M70" s="6" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="N70" s="6" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O67" s="6" t="inlineStr">
+      <c r="O70" s="6" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P67" s="6" t="inlineStr">
+      <c r="P70" s="6" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>**P1**</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Integrated Smart Systems</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K68" s="8" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="L68" s="8" t="inlineStr">
+      <c r="L71" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="M68" s="8" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
-      <c r="O68" s="8" t="inlineStr"/>
-      <c r="P68" s="8" t="inlineStr"/>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr"/>
+      <c r="O71" s="8" t="inlineStr"/>
+      <c r="P71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>**P2**</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>Cloud Infrastructure &amp; Cybersecurity</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr"/>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr"/>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr"/>
+      <c r="K72" s="10" t="inlineStr"/>
+      <c r="L72" s="10" t="inlineStr"/>
+      <c r="M72" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O69" s="10" t="inlineStr"/>
-      <c r="P69" s="10" t="inlineStr"/>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="O72" s="10" t="inlineStr"/>
+      <c r="P72" s="10" t="inlineStr"/>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>**P3**</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>Digital Platform Engineering</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-      <c r="M70" s="8" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="P70" s="8" t="inlineStr">
+      <c r="P73" s="8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="74"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>6. MATRIKS KESELARASAN CPL ↔ VISI KEILMUAN VMTS 2045</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="5" t="n"/>
-    </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="5" t="n"/>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>Elemen Kunci VMTS SISTEKIN 2045</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>CPL yang Selaras &amp; Mengakomodasi</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>*"Sistem dan teknologi informasi cerdas"*</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>`P1`, `P2`, `KK1`, `KK2`</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>*"Terintegrasi kecerdasan artifisial"*</t>
         </is>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>`P1`, `P2`, `KK1`, `KK2`, `KK3`</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>*"Technopreneurship berbasis kebutuhan masyarakat"*</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>`P2`, `KK5`, `KK6`</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>*"Bermutu, mandiri, dan bermartabat"*</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>`S1`, `KU1`, `KU3`, `P3`, `KK4`</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>*"Berwawasan global"*</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>`KU2`, `P3`, `KK3`, `KK5`</t>
         </is>
@@ -3182,13 +3308,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:P42"/>
-    <mergeCell ref="A66:P66"/>
+    <mergeCell ref="A44:P44"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A69:P69"/>
+    <mergeCell ref="A62:P62"/>
     <mergeCell ref="A20:P20"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A59:P59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
